--- a/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
+++ b/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
@@ -397,31 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>الاسم الأول *</v>
+        <v>الاسم الأول</v>
       </c>
       <c r="B1" t="str">
-        <v>الكنية *</v>
+        <v>الكنية</v>
       </c>
       <c r="C1" t="str">
         <v>الاسم بالعربية</v>
@@ -462,57 +445,13 @@
       <c r="O1" t="str">
         <v>معرّف الجمعية الأوروبية</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>محمد</v>
-      </c>
-      <c r="B2" t="str">
-        <v>الأحمد</v>
-      </c>
-      <c r="C2" t="str">
-        <v>محمد علي الأحمد</v>
-      </c>
-      <c r="D2" t="str">
-        <v>علي</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Mohammad Al-Ahmad</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1985-06-15</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiology</v>
-      </c>
-      <c r="I2" t="str">
-        <v>example@email.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>0911234567</v>
-      </c>
-      <c r="K2" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L2" t="str">
-        <v>مستشفى المجتهد</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2020-01-01</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
+      <c r="P1" t="str">
+        <v>تاريخ التسجيل</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
+++ b/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,159 @@
         <v>تاريخ التسجيل</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B2" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H2" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L2" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N2" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-05T17:26:35.077Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B3" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D3" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E3" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G3" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H3" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I3" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J3" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K3" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L3" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N3" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v>2026-05-05T17:35:01.976Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B4" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D4" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E4" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G4" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H4" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I4" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J4" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K4" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L4" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N4" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v>2026-05-05T17:35:59.270Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
+++ b/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -599,9 +599,59 @@
         <v>2026-05-05T17:35:59.270Z</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B5" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D5" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E5" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G5" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H5" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I5" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J5" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K5" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L5" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N5" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>2026-05-05T17:40:38.322Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
+++ b/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -649,9 +649,109 @@
         <v>2026-05-05T17:40:38.322Z</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B6" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D6" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E6" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G6" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H6" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I6" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J6" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K6" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L6" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N6" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>2026-05-05T17:53:23.829Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ابراهيم</v>
+      </c>
+      <c r="B7" t="str">
+        <v>الصيداوي</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D7" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="E7" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G7" t="str">
+        <v>ذكر</v>
+      </c>
+      <c r="H7" t="str">
+        <v>جراحة قلب</v>
+      </c>
+      <c r="I7" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J7" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K7" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="L7" t="str">
+        <v>دمشق</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N7" t="str">
+        <v>عضو أصيل</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>2026-05-05T17:57:20.590Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
+++ b/docs/form_by_n8n/نموذج-الأعضاء-عربي.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,309 +449,9 @@
         <v>تاريخ التسجيل</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B2" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H2" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L2" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N2" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-05T17:26:35.077Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B3" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D3" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E3" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F3" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G3" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H3" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I3" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J3" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K3" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L3" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N3" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>2026-05-05T17:35:01.976Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B4" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D4" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E4" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F4" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G4" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H4" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I4" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J4" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K4" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L4" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N4" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>2026-05-05T17:35:59.270Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B5" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C5" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D5" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E5" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F5" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G5" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H5" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I5" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J5" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K5" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L5" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N5" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>2026-05-05T17:40:38.322Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B6" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D6" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E6" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F6" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G6" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H6" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I6" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J6" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K6" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L6" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N6" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>2026-05-05T17:53:23.829Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ابراهيم</v>
-      </c>
-      <c r="B7" t="str">
-        <v>الصيداوي</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D7" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="E7" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F7" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G7" t="str">
-        <v>ذكر</v>
-      </c>
-      <c r="H7" t="str">
-        <v>جراحة قلب</v>
-      </c>
-      <c r="I7" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J7" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K7" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="L7" t="str">
-        <v>دمشق</v>
-      </c>
-      <c r="M7" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N7" t="str">
-        <v>عضو أصيل</v>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>2026-05-05T17:57:20.590Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>